--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-09-29
-含首尾；导出时间（北京）2026-09-29 13:57</t>
+含首尾；导出时间（北京）2026-09-29 14:01</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-29 13:57:07</t>
+          <t>2026-09-29 14:01:58</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-09-29
-含首尾；导出时间（北京）2026-09-29 14:01</t>
+含首尾；导出时间（北京）2026-09-29 14:09</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-29 14:01:58</t>
+          <t>2026-09-29 14:09:22</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-09-29
-含首尾；导出时间（北京）2026-09-29 14:09</t>
+含首尾；导出时间（北京）2026-09-29 16:05</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-29 14:09:22</t>
+          <t>2026-09-29 16:05:37</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-09-29
-含首尾；导出时间（北京）2026-09-29 16:05</t>
+含首尾；导出时间（北京）2026-09-29 16:40</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-29 16:05:37</t>
+          <t>2026-09-29 16:40:39</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-09-29
-含首尾；导出时间（北京）2026-09-29 16:40</t>
+含首尾；导出时间（北京）2026-09-29 16:43</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-29 16:40:39</t>
+          <t>2026-09-29 16:43:58</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-09-29
-含首尾；导出时间（北京）2026-09-29 16:43</t>
+          <t>原始发布日期：1900-01-01 至 2026-09-30
+含首尾；导出时间（北京）2026-09-30 11:28</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-09-29（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-09-30（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-09-29（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-09-30（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-09-29（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-09-30（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-09-29（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-09-30（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-09-29（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-09-30（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43:58</t>
+          <t>2026-09-30 11:28:39</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-09-30
-含首尾；导出时间（北京）2026-09-30 11:28</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-13
+含首尾；导出时间（北京）2026-10-13 09:43</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-09-30（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-13（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-09-30（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-13（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-09-30（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-13（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-09-30（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-13（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-09-30（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-13（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-09-30 11:28:39</t>
+          <t>2026-10-13 09:43:29</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-10-13
-含首尾；导出时间（北京）2026-10-13 09:43</t>
+含首尾；导出时间（北京）2026-10-13 09:46</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-13 09:43:29</t>
+          <t>2026-10-13 09:46:19</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-10-13
-含首尾；导出时间（北京）2026-10-13 09:46</t>
+含首尾；导出时间（北京）2026-10-13 10:29</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-13 09:46:19</t>
+          <t>2026-10-13 10:29:18</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-10-13
-含首尾；导出时间（北京）2026-10-13 10:29</t>
+含首尾；导出时间（北京）2026-10-13 16:03</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-13 10:29:18</t>
+          <t>2026-10-13 16:03:22</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -931,7 +931,7 @@
       <c r="E1" s="46" t="inlineStr">
         <is>
           <t>原始发布日期：1900-01-01 至 2026-10-13
-含首尾；导出时间（北京）2026-10-13 16:03</t>
+含首尾；导出时间（北京）2026-10-13 21:35</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-13 16:03:22</t>
+          <t>2026-10-13 21:35:04</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-13
-含首尾；导出时间（北京）2026-10-13 21:35</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-14
+含首尾；导出时间（北京）2026-10-14 16:46</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-13（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-14（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-13（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-14（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-13（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-14（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-13（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-14（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-13（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-14（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-13 21:35:04</t>
+          <t>2026-10-14 16:46:39</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-14
-含首尾；导出时间（北京）2026-10-14 16:46</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-15
+含首尾；导出时间（北京）2026-10-15 16:38</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-14（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-15（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-14（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-15（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-14（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-15（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-14（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-15（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-14（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-15（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-14 16:46:39</t>
+          <t>2026-10-15 16:38:30</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-15
-含首尾；导出时间（北京）2026-10-15 16:38</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-16
+含首尾；导出时间（北京）2026-10-16 16:32</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-15（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-16（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-15（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-16（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-15（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-16（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-15（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-16（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-15（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-16（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-15 16:38:30</t>
+          <t>2026-10-16 16:32:21</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-16
-含首尾；导出时间（北京）2026-10-16 16:32</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-17
+含首尾；导出时间（北京）2026-10-17 16:15</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-16（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-17（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-16（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-17（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-16（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-17（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-16（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-17（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-16（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-17（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-16 16:32:21</t>
+          <t>2026-10-17 16:15:35</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-17
-含首尾；导出时间（北京）2026-10-17 16:15</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-18
+含首尾；导出时间（北京）2026-10-18 16:30</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-17（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-18（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-17（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-18（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-17（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-18（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-17（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-18（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-17（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-18（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-17 16:15:35</t>
+          <t>2026-10-18 16:30:42</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-18
-含首尾；导出时间（北京）2026-10-18 16:30</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-19
+含首尾；导出时间（北京）2026-10-19 16:49</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-18（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-19（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-18（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-19（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-18（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-19（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-18（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-19（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-18（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-19（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-18 16:30:42</t>
+          <t>2026-10-19 16:49:30</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-19
-含首尾；导出时间（北京）2026-10-19 16:49</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-20
+含首尾；导出时间（北京）2026-10-20 16:36</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-19（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-20（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-19（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-20（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-19（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-20（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-19（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-20（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-19（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-20（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-19 16:49:30</t>
+          <t>2026-10-20 16:36:00</t>
         </is>
       </c>
     </row>

--- a/exports/baseline.xlsx
+++ b/exports/baseline.xlsx
@@ -930,8 +930,8 @@
       </c>
       <c r="E1" s="46" t="inlineStr">
         <is>
-          <t>原始发布日期：1900-01-01 至 2026-10-20
-含首尾；导出时间（北京）2026-10-20 16:36</t>
+          <t>原始发布日期：1900-01-01 至 2026-10-21
+含首尾；导出时间（北京）2026-10-21 16:47</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-20（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-21（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D37" s="20" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-20（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-21（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D42" s="44" t="n"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C48" s="49" t="inlineStr">
         <is>
-          <t>原始发布日期 1900-01-01—2026-10-20（含首尾）；官方出处及完整证据见政策明细。</t>
+          <t>原始发布日期 1900-01-01—2026-10-21（含首尾）；官方出处及完整证据见政策明细。</t>
         </is>
       </c>
       <c r="D48" s="45" t="n"/>
@@ -2178,7 +2178,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-20（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <oddFooter>&amp;C原发日期 1900-01-01 至 2026-10-21（含两端）&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>1900-01-01 至 2026-10-20（含起止两日，闭区间；不按转载日期筛选）</t>
+          <t>1900-01-01 至 2026-10-21（含起止两日，闭区间；不按转载日期筛选）</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B7" s="59" t="inlineStr">
         <is>
-          <t>2026-10-20 16:36:00</t>
+          <t>2026-10-21 16:47:50</t>
         </is>
       </c>
     </row>
